--- a/tools/review-checklists/詳細設計レビュー観点.xlsx
+++ b/tools/review-checklists/詳細設計レビュー観点.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1464,8 +1464,84 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>画面一覧</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>画面の一覧に漏れや重複がない</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>画面一覧シートの画面IDに重複がなく、すべての画面に画面名・画面区分・概要が記入されている。</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>*画面一覧*</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>画面一覧</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>画面遷移の遷移元・遷移先が画面一覧と一致している</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>画面遷移シートの遷移元画面ID・遷移先画面IDがすべて画面一覧シートにあり、画面名が画面一覧シートと一致している。</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>*画面一覧*</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H26"/>
+  <autoFilter ref="A1:H28"/>
   <dataValidations count="2">
     <dataValidation sqref="E2:E225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>

--- a/tools/review-checklists/詳細設計レビュー観点.xlsx
+++ b/tools/review-checklists/詳細設計レビュー観点.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$1:$J$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -466,6 +466,8 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,6 +511,16 @@
           <t>有効</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>確かめ方</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ツールの確認</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -547,6 +559,16 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>両方</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>版数</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -585,6 +607,16 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>両方</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>残っている文言</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -623,26 +655,36 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>両方</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>表記ゆれ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>画面項目</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>入力項目の定義に漏れがない</t>
+          <t>設計書どうしの ID と属性が食い違っていない</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>入出力が I または IO の項目すべてに、型・必須・入力チェックが記入されている。型が文字・半角英数・数値の項目には桁数が記入されている。</t>
+          <t>参照しているテーブル・カラム・メッセージ・コード・画面・IF の ID が、すべて定義されている。同じ ID を 2 か所で定義していない。シートのヘッダ・ファイル名の ID と名前がそろっている。画面項目・IF の項目の型・桁数・必須が、参照先のカラムと合っている。テーブル一覧とテーブル定義書のテーブルが一致している。</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -652,20 +694,30 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>*画面設計書*</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>○</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>参照先なし、重複定義、ヘッダの違い、属性の違い、一覧との違い（テーブル）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -675,17 +727,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>入力チェックのエラー時のメッセージが決まっている</t>
+          <t>入力項目の定義に漏れがない</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>入力チェック欄に書かれたチェックそれぞれに、エラー時のメッセージIDが記載されている。</t>
+          <t>入出力が I または IO の項目すべてに、型・必須・入力チェックが記入されている。型が文字・半角英数・数値の項目には桁数が記入されている。</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -699,11 +751,21 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>両方</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>入力項目の型・桁数</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -713,17 +775,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>選択項目・日付項目の初期値が決まっている</t>
+          <t>入力チェックのエラー時のメッセージが決まっている</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>区分が選択・日付・チェックボックスの入力項目に初期値が記入されている（初期値なしの場合は「なし」と明記されている）。</t>
+          <t>入力チェック欄に書かれたチェックそれぞれに、エラー時のメッセージIDが記載されている。</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -737,31 +799,41 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>入力チェックのメッセージ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>イベント</t>
+          <t>画面項目</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>画面上の操作すべてにイベントが定義されている</t>
+          <t>選択項目・日付項目の初期値が決まっている</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>画面項目定義の区分がボタン・リンクの項目それぞれに、対応するイベントがイベント定義にある。</t>
+          <t>区分が選択・日付・チェックボックスの入力項目に初期値が記入されている（初期値なしの場合は「なし」と明記されている）。</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -775,11 +847,21 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>初期値</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -789,12 +871,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>更新系イベントに確認・完了・排他制御の記載がある</t>
+          <t>画面上の操作すべてにイベントが定義されている</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>使用テーブルに C・U・D を含むイベントの処理概要に、実行前の確認メッセージ、完了メッセージ、他ユーザーが先に更新していた場合（排他制御）の扱いが記載されている。</t>
+          <t>画面項目定義の区分がボタン・リンクの項目それぞれに、対応するイベントがイベント定義にある。</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -813,11 +895,21 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>ボタンのイベント</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -827,17 +919,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>処理手順と異常時の動きが書かれている</t>
+          <t>更新系イベントに確認・完了・排他制御の記載がある</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>処理概要が番号付きの手順で書かれ、チェックエラー・該当データなし・0件などの異常時に、何を表示してどう中断するかが記載されている。</t>
+          <t>使用テーブルに C・U・D を含むイベントの処理概要に、実行前の確認メッセージ、完了メッセージ、他ユーザーが先に更新していた場合（排他制御）の扱いが記載されている。</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -851,11 +943,17 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -865,12 +963,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>処理概要とメッセージ欄が一致している</t>
+          <t>処理手順と異常時の動きが書かれている</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>処理概要に出てくるメッセージIDがすべてメッセージ欄に記載され、メッセージ欄のIDがすべて処理概要か入力チェックのどこかで使われている。</t>
+          <t>処理概要が番号付きの手順で書かれ、チェックエラー・該当データなし・0件などの異常時に、何を表示してどう中断するかが記載されている。</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,11 +987,17 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -903,12 +1007,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>処理概要と使用テーブルが一致している</t>
+          <t>処理概要とメッセージ欄が一致している</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>処理概要で検索・登録・更新・削除しているテーブルが使用テーブル欄に CRUD 付きで記載され、使用テーブル欄にあるテーブルは処理概要で使われている。</t>
+          <t>処理概要に出てくるメッセージIDがすべてメッセージ欄に記載され、メッセージ欄のIDがすべて処理概要か入力チェックのどこかで使われている。</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -927,26 +1031,36 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>メッセージ欄</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>画面遷移</t>
+          <t>イベント</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>遷移先と引き渡し項目が決まっている</t>
+          <t>処理概要と使用テーブルが一致している</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>遷移するイベントは遷移先の画面IDが記載され、画面概要の遷移先の表にも同じ遷移が引き渡し項目付きで記載されている。</t>
+          <t>処理概要で検索・登録・更新・削除しているテーブルが使用テーブル欄に CRUD 付きで記載され、使用テーブル欄にあるテーブルは処理概要で使われている。</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -965,26 +1079,32 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>メッセージ</t>
+          <t>画面遷移</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>使用するメッセージが場面に合っている</t>
+          <t>遷移先と引き渡し項目が決まっている</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>イベント定義・入力チェックで使っているメッセージIDが参照資料のメッセージ一覧に存在し、メッセージの文言と種別（エラー・確認など）がその場面に合っている。</t>
+          <t>遷移するイベントは遷移先の画面IDが記載され、画面概要の遷移先の表にも同じ遷移が引き渡し項目付きで記載されている。</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -997,59 +1117,75 @@
           <t>*画面設計書*</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>*メッセージ一覧*</t>
-        </is>
-      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>○</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>両方</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>組み合わせの違い</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T01</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>テーブル</t>
+          <t>メッセージ</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>全テーブルに主キーがある</t>
+          <t>使用するメッセージが場面に合っている</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>テーブルごとのシートで、PK 欄に 1 つ以上の列が指定されている。</t>
+          <t>イベント定義・入力チェックで使っているメッセージIDが参照資料のメッセージ一覧に存在し、メッセージの文言と種別（エラー・確認など）がその場面に合っている。</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>*テーブル定義書*</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>*画面設計書*</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>*メッセージ一覧*</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,12 +1195,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>型と桁数が定義されている</t>
+          <t>全テーブルに主キーがある</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>CHAR・VARCHAR・NUMERIC の列に桁数があり、NUMERIC の列は小数の桁数も記入されている。</t>
+          <t>テーブルごとのシートで、PK 欄に 1 つ以上の列が指定されている。</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1083,11 +1219,21 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>主キー</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1097,17 +1243,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>必須列の値の決まり方が分かる</t>
+          <t>型と桁数が定義されている</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>必須（NOT NULL）の列のうち、画面や処理から必ず値が入るとは限らない列に、デフォルト値または備考での説明がある。</t>
+          <t>CHAR・VARCHAR・NUMERIC の列に桁数があり、NUMERIC の列は小数の桁数も記入されている。</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1121,11 +1267,21 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>カラムの型・桁数</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1135,12 +1291,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>共通の管理列がある</t>
+          <t>必須列の値の決まり方が分かる</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>全テーブルに登録日時・登録者・更新日時・更新者と、排他制御用の列（バージョン番号など）がある。</t>
+          <t>必須（NOT NULL）の列のうち、画面や処理から必ず値が入るとは限らない列に、デフォルト値または備考での説明がある。</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1159,11 +1315,17 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1173,17 +1335,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>コード値を持つ列にコード定義が示されている</t>
+          <t>共通の管理列がある</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>区分・ステータス・フラグなどコード値を持つ列の備考に、コード定義のコード区分IDが記載されている。</t>
+          <t>全テーブルに登録日時・登録者・更新日時・更新者と、排他制御用の列（バージョン番号など）がある。</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1197,11 +1359,17 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1211,17 +1379,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>外部キー列にインデックスが検討されている</t>
+          <t>コード値を持つ列にコード定義が示されている</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>外部キー参照先がある列（複合主キーの先頭列を除く）に、インデックスがあるか、不要な理由が記載されている。</t>
+          <t>区分・ステータス・フラグなどコード値を持つ列の備考に、コード定義のコード区分IDが記載されている。</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1235,36 +1403,42 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>I01</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IF</t>
+          <t>テーブル</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>連携の条件が漏れなく決まっている</t>
+          <t>外部キー列にインデックスが検討されている</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>IF概要に、連携方式・タイミング・ファイル名・形式・文字コード・改行・抽出条件・後処理・0件時・エラー時の扱いが記載されている。</t>
+          <t>外部キー参照先がある列（複合主キーの先頭列を除く）に、インデックスがあるか、不要な理由が記載されている。</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>*IF定義書*</t>
+          <t>*テーブル定義書*</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1273,11 +1447,17 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>I02</t>
+          <t>I01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1287,12 +1467,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>レコードの全項目が定義されている</t>
+          <t>連携の条件が漏れなく決まっている</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>レコード定義の全項目に属性・桁数・必須・設定元が記入され、日付と数値の項目は編集形式（yyyyMMdd、ゼロ埋めの有無など）が明記されている。</t>
+          <t>IF概要に、連携方式・タイミング・ファイル名・形式・文字コード・改行・抽出条件・後処理・0件時・エラー時の扱いが記載されている。</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1311,11 +1491,17 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>I03</t>
+          <t>I02</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1325,17 +1511,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>データ例がレコード定義と一致している</t>
+          <t>レコードの全項目が定義されている</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>データ例の項目数・並び順・日付の形式・空欄の扱いが、レコード定義と一致している。</t>
+          <t>レコード定義の全項目に属性・桁数・必須・設定元が記入され、日付と数値の項目は編集形式（yyyyMMdd、ゼロ埋めの有無など）が明記されている。</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1349,36 +1535,42 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>I03</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>メッセージ</t>
+          <t>IF</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>パラメータの説明がある</t>
+          <t>データ例がレコード定義と一致している</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>{0} などのパラメータを含むメッセージは、パラメータ欄に何が入るかが説明されている。</t>
+          <t>データ例の項目数・並び順・日付の形式・空欄の扱いが、レコード定義と一致している。</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>*メッセージ一覧*</t>
+          <t>*IF定義書*</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -1387,11 +1579,17 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>M01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1401,12 +1599,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>利用者に分かる文言になっている</t>
+          <t>パラメータの説明がある</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>メッセージに内部名称（テーブル名・項目ID・例外名など）が含まれず、エラーの場合は利用者が次に何をすればよいか分かる。</t>
+          <t>{0} などのパラメータを含むメッセージは、パラメータ欄に何が入るかが説明されている。</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1425,26 +1623,32 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>K01</t>
+          <t>M02</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>コード</t>
+          <t>メッセージ</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>コード値の定義が明確である</t>
+          <t>利用者に分かる文言になっている</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>コード区分ごとに初期値（既定値）が分かり、コード値の重複や、表示名が同じコード値がない。</t>
+          <t>メッセージに内部名称（テーブル名・項目ID・例外名など）が含まれず、エラーの場合は利用者が次に何をすればよいか分かる。</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1454,7 +1658,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>*コード定義書*</t>
+          <t>*メッセージ一覧*</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
@@ -1463,36 +1667,42 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>L01</t>
+          <t>K01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>画面一覧</t>
+          <t>コード</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>画面の一覧に漏れや重複がない</t>
+          <t>コード値の定義が明確である</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>画面一覧シートの画面IDに重複がなく、すべての画面に画面名・画面区分・概要が記入されている。</t>
+          <t>コード区分ごとに初期値（既定値）が分かり、コード値の重複や、表示名が同じコード値がない。</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>*画面一覧*</t>
+          <t>*コード定義書*</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -1501,11 +1711,17 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>L01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1515,17 +1731,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>画面遷移の遷移元・遷移先が画面一覧と一致している</t>
+          <t>画面の一覧に漏れや重複がない</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>画面遷移シートの遷移元画面ID・遷移先画面IDがすべて画面一覧シートにあり、画面名が画面一覧シートと一致している。</t>
+          <t>画面一覧シートの画面IDに重複がなく、すべての画面に画面名・画面区分・概要が記入されている。</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1539,15 +1755,76 @@
           <t>○</t>
         </is>
       </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>両方</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>一覧との違い（画面）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>画面一覧</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>画面遷移の遷移元・遷移先が画面一覧と一致している</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>画面遷移シートの遷移元画面ID・遷移先画面IDがすべて画面一覧シートにあり、画面名が画面一覧シートと一致している。</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>*画面一覧*</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>両方</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>組み合わせの違い</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H28"/>
-  <dataValidations count="2">
+  <autoFilter ref="A1:J29"/>
+  <dataValidations count="3">
     <dataValidation sqref="E2:E225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"○,×"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"AI,ツール,両方"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1560,7 +1837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1640,10 +1917,174 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>確かめ方：AI／ツール／両方。ツールの観点は AI に依頼せず、「ツールの確認」に書いた確認をツールで行います。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　両方の観点は AI にも依頼します（ツールで確かめる分は、AI には指摘しなくてよいと伝えます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　空欄なら、ツールの確認があれば両方、無ければ AI です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ツールの確認：ツールで行う確認の名前（複数ある場合は「,」区切り）。使える名前は下の一覧のとおりです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　数える・突き合わせるだけで決まる観点は、ツールのほうが漏れが無く、AI への依頼も減ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>■ ツールの確認の一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>版数　　　　　　　　　　：表紙・改訂履歴・ファイル名の版数と更新日の食い違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>残っている文言　　　　　：TODO・TBD・未定・検討中などの消し忘れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>表記ゆれ　　　　　　　　：カタカナの長音（ー）や全角・半角の表記ゆれ（-Glossary の用語集の揺れも）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>参照先なし　　　　　　　：定義されていない ID（テーブル・メッセージ・画面など）の参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>重複定義　　　　　　　　：同じ ID の重複した定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>一覧との違い　　　　　　：画面一覧・テーブル一覧と設計書の過不足・名前の違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>ヘッダの違い　　　　　　：シートのヘッダ・ファイル名の ID と名前の食い違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>組み合わせの違い　　　　：画面遷移の一覧・イベント定義の遷移先・画面概要の遷移先の食い違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>属性の違い　　　　　　　：画面項目・IF の項目と、参照先のカラムの型・桁数・必須の違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　上の 6 つ（設計書どうしの食い違い）は、「参照先なし（メッセージ）」のように（ ）で種類を付けると、その種類だけにします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>入力項目の型・桁数　　　：入力項目の型の空欄と、文字・数値の型の桁数の空欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>入力チェックのメッセージ：メッセージIDの無い入力チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>初期値　　　　　　　　　：選択・日付・チェックボックスの入力項目の初期値の空欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>ボタンのイベント　　　　：イベント定義の無いボタン・リンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>メッセージ欄　　　　　　：イベントの処理概要とメッセージ欄のメッセージIDの過不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>主キー　　　　　　　　　：主キーの無いテーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>カラムの型・桁数　　　　：カラムの型の空欄と、桁数・小数の要る型の桁数・小数の空欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>観点の追加・変更は自由です。既定の観点は、架空の詳細設計サンプル（docs/design-sample）を想定した一般的な例です。</t>
         </is>
